--- a/public/Template_Lulusan.xlsx
+++ b/public/Template_Lulusan.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>program_studi</t>
   </si>
@@ -44,6 +44,9 @@
     <t>token</t>
   </si>
   <si>
+    <t>no_tlpn</t>
+  </si>
+  <si>
     <t>D4 Teknik Informatika</t>
   </si>
   <si>
@@ -51,6 +54,9 @@
   </si>
   <si>
     <t>2025-07-15</t>
+  </si>
+  <si>
+    <t>085123456789</t>
   </si>
 </sst>
 </file>
@@ -224,12 +230,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -569,7 +581,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -593,16 +605,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -611,94 +623,99 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1045,17 +1062,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="24.5555555555556" customWidth="1"/>
     <col min="2" max="2" width="11.7777777777778" customWidth="1"/>
     <col min="3" max="3" width="20.5555555555556" customWidth="1"/>
     <col min="4" max="4" width="13.1111111111111" customWidth="1"/>
     <col min="5" max="5" width="7.66666666666667" customWidth="1"/>
+    <col min="6" max="6" width="14.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1071,22 +1089,28 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3">
         <v>2198653400</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2">
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3">
         <v>123456</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
